--- a/output/pdf_financials_xlsx/PX.xlsx
+++ b/output/pdf_financials_xlsx/PX.xlsx
@@ -1310,13 +1310,13 @@
         <v>-1.361847</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1.387793</v>
+        <v>-1.387793</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.755514</v>
+        <v>-0.755514</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.886138</v>
+        <v>-0.886138</v>
       </c>
     </row>
     <row r="17">
@@ -1594,13 +1594,13 @@
         <v>-1.361847</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>1.387793</v>
+        <v>-1.387793</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.755514</v>
+        <v>-0.755514</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.886138</v>
+        <v>-0.886138</v>
       </c>
     </row>
     <row r="21">
@@ -1759,13 +1759,13 @@
         <v>-1.361847</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.387793</v>
+        <v>-1.387793</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.755514</v>
+        <v>-0.755514</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>0.886138</v>
+        <v>-0.886138</v>
       </c>
     </row>
     <row r="24">
@@ -2047,13 +2047,13 @@
         <v>-1.363245</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.384937</v>
+        <v>-1.390649</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.755514</v>
+        <v>-0.755514</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.886138</v>
+        <v>-0.886138</v>
       </c>
     </row>
     <row r="28">
@@ -2157,13 +2157,13 @@
         <v>-1.363245</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1.384937</v>
+        <v>-1.390649</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.75584</v>
+        <v>-0.755188</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.886143</v>
+        <v>-0.8861329999999999</v>
       </c>
     </row>
     <row r="30">
@@ -2299,13 +2299,13 @@
         <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5753,10 +5753,10 @@
         <v>0</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.472678</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.481256</v>
       </c>
     </row>
     <row r="93">
@@ -6096,10 +6096,10 @@
         <v>-1.387793</v>
       </c>
       <c r="P99" s="3" t="n">
-        <v>0.755514</v>
+        <v>-0.755514</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>0.886138</v>
+        <v>-0.886138</v>
       </c>
     </row>
     <row r="100">
@@ -9252,7 +9252,11 @@
           <t>Reserve for warrants 10</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -37622,10 +37626,10 @@
         </is>
       </c>
       <c r="S313" s="5" t="n">
-        <v>0.755514</v>
+        <v>-0.755514</v>
       </c>
       <c r="T313" s="5" t="n">
-        <v>0.886138</v>
+        <v>-0.886138</v>
       </c>
     </row>
     <row r="314">
@@ -38763,10 +38767,10 @@
         </is>
       </c>
       <c r="R325" s="5" t="n">
-        <v>1.387793</v>
+        <v>-1.387793</v>
       </c>
       <c r="S325" s="5" t="n">
-        <v>0.755514</v>
+        <v>-0.755514</v>
       </c>
       <c r="T325" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/PX.xlsx
+++ b/output/pdf_financials_xlsx/PX.xlsx
@@ -965,22 +965,22 @@
         <v>0.807723</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.235882</v>
+        <v>0.729082</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.244359</v>
+        <v>1.392149</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.241142</v>
+        <v>1.527636</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.218314</v>
+        <v>3.047092</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.278741</v>
+        <v>1.827623</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.481608</v>
+        <v>1.615767</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.349337</v>
@@ -2418,43 +2418,43 @@
         <v>3.300209</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.830351</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.830351</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.190954</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.261259</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.081071</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.578815</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.014968</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.392267</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.7146439999999999</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.603638</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.23435</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.225341</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>4.675317</v>
       </c>
     </row>
     <row r="35">
@@ -2528,43 +2528,43 @@
         <v>3.300209</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.830351</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.830351</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.190954</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.261259</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.081071</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.578815</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.014968</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.392267</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.7146439999999999</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.603638</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.23435</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.225341</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>4.675317</v>
       </c>
     </row>
     <row r="37">
@@ -3188,43 +3188,43 @@
         <v>0.114421</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.873399</v>
+        <v>0.043048</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.916399</v>
+        <v>0.086048</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.27923</v>
+        <v>0.08827599999999999</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.311027</v>
+        <v>0.049768</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.106007</v>
+        <v>0.024936</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.587344</v>
+        <v>0.008529</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.147169</v>
+        <v>0.132201</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.5928870000000001</v>
+        <v>0.20062</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.167319</v>
+        <v>0.452675</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.939167</v>
+        <v>0.335529</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.497437</v>
+        <v>0.263087</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.430869</v>
+        <v>0.205528</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>5.43618</v>
+        <v>0.760863</v>
       </c>
     </row>
     <row r="49">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16654,7 +16654,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -39992,7 +39992,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -41810,7 +41810,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">

--- a/output/pdf_financials_xlsx/PX.xlsx
+++ b/output/pdf_financials_xlsx/PX.xlsx
@@ -776,16 +776,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.228298</v>
+        <v>0.2379</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.595274</v>
+        <v>0.656664</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.718614</v>
+        <v>0.7982629999999999</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.6519</v>
+        <v>0.693595</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0.373901</v>
@@ -1326,19 +1326,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.262</v>
+        <v>-0.262</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.167</v>
+        <v>-0.167</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>0.168</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-1.632</v>
+        <v>1.632</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.146</v>
+        <v>-0.146</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>0</v>
+        <v>2.415952</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0</v>
+        <v>1.788</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>0</v>
@@ -2491,10 +2491,10 @@
         <v>0</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0</v>
+        <v>0.123672</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0</v>
+        <v>0.153919</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>0</v>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.379937</v>
+        <v>2.795889</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>7.178564</v>
+        <v>8.966564</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>3.300209</v>
@@ -2546,10 +2546,10 @@
         <v>0.578815</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.014968</v>
+        <v>1.13864</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.392267</v>
+        <v>0.5461859999999999</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.7146439999999999</v>
@@ -2613,7 +2613,7 @@
         <v>0.080995</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0</v>
+        <v>0.007993999999999999</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>0.012111</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>0</v>
+        <v>0.424</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.013764</v>
+        <v>0.437764</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>0.038424</v>
@@ -2833,7 +2833,7 @@
         <v>0.080995</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>0</v>
+        <v>0.007993999999999999</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.012111</v>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.877134</v>
+        <v>0.037182</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.92364</v>
+        <v>0.13564</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.114421</v>
@@ -3206,10 +3206,10 @@
         <v>0.008529</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.132201</v>
+        <v>0.008529</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.20062</v>
+        <v>0.046701</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.452675</v>
@@ -3218,7 +3218,7 @@
         <v>0.335529</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.263087</v>
+        <v>0.255093</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.205528</v>
@@ -3322,13 +3322,13 @@
         <v>0</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>0</v>
+        <v>0.362548</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>0</v>
+        <v>0.326311</v>
       </c>
       <c r="O50" s="3" t="n">
-        <v>0</v>
+        <v>0.239543</v>
       </c>
       <c r="P50" s="3" t="n">
         <v>0.185115</v>
@@ -3457,37 +3457,37 @@
         <v>0</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>0.21534</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0</v>
+        <v>0.266054</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0</v>
+        <v>0.245194</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0</v>
+        <v>0.245194</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0</v>
+        <v>0.130104</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0</v>
+        <v>0.04857</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0</v>
+        <v>0.036495</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0</v>
+        <v>0.031279</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0</v>
+        <v>0.023822</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0</v>
+        <v>0.017178</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>0</v>
+        <v>0.009915</v>
       </c>
       <c r="N53" s="3" t="n">
         <v>0.007617</v>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>0</v>
+        <v>0.095485</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0</v>
+        <v>0.21534</v>
       </c>
       <c r="D58" s="3" t="n">
         <v>0</v>
@@ -3959,10 +3959,10 @@
         <v>0.017178</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.009915</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>0.007617</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3" t="n">
         <v>0</v>
@@ -4362,7 +4362,7 @@
         <v>0.607123</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0</v>
+        <v>0.970338</v>
       </c>
       <c r="P68" s="3" t="n">
         <v>0.92138</v>
@@ -4411,13 +4411,13 @@
         <v>0</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="P69" s="3" t="n">
         <v>0</v>
@@ -4521,13 +4521,13 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="P71" s="3" t="n">
         <v>0</v>
@@ -4741,13 +4741,13 @@
         <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>1.129847</v>
+        <v>0.119509</v>
       </c>
       <c r="P75" s="3" t="n">
         <v>0</v>
@@ -5049,20 +5049,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M80" s="3" t="n">
+        <v>0.08238114460362313</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.1050817536043041</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>-0.06325010673455511</v>
       </c>
       <c r="P80" s="1" t="inlineStr">
         <is>
@@ -5711,13 +5705,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.27595</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.646641</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.670769</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -6362,7 +6356,7 @@
         <v>-0.07983800000000001</v>
       </c>
       <c r="M104" s="3" t="n">
-        <v>0.079912</v>
+        <v>0.153916</v>
       </c>
       <c r="N104" s="3" t="n">
         <v>-0.01876</v>
@@ -6527,13 +6521,13 @@
         <v>0.055529</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>0.334072</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>0.150436</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>0.024547</v>
       </c>
       <c r="P107" s="3" t="n">
         <v>0</v>
@@ -6912,7 +6906,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>0</v>
+        <v>-0.033216</v>
       </c>
       <c r="N114" s="3" t="n">
         <v>0</v>
@@ -10100,7 +10094,11 @@
           <t>Amounts receivable, note 5</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -10268,7 +10266,11 @@
           <t>Investments, note 6</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -10632,7 +10634,11 @@
           <t>Accounts payable and accrued liabilities, note 10 &amp; 11</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -10822,7 +10828,11 @@
           <t>Loan repayable, note 12</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -11008,7 +11018,11 @@
           <t>Loan repayable, note 12</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -11938,7 +11952,11 @@
           <t>Equipment, note 8</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -12222,7 +12240,11 @@
           <t>Loan repayable, note 15</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -13158,7 +13180,11 @@
           <t>Marketable securities, note 7</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -13252,7 +13278,11 @@
           <t>Equipment, note 9</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -15050,7 +15080,11 @@
           <t>Equipment, note 7</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -16946,7 +16980,11 @@
           <t>Equipment, note 8 130,104</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -19248,7 +19286,11 @@
           <t>Marketable securities, note 5</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -19344,7 +19386,11 @@
           <t>Equipment, note 6</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -19818,7 +19864,11 @@
           <t>Contributed surplus, note 8 (c)</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -20298,7 +20348,11 @@
           <t>Loan receivable, note 7</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>LoansReceivable</t>
+        </is>
+      </c>
       <c r="E129" s="5" t="n">
         <v>0.424</v>
       </c>
@@ -20394,7 +20448,11 @@
           <t>Marketable securities, note 6</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E130" s="5" t="n">
         <v>2.415952</v>
       </c>
@@ -20488,7 +20546,11 @@
           <t>Property and equipment, note 8</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E131" s="5" t="n">
         <v>0.095485</v>
       </c>
@@ -20960,7 +21022,11 @@
           <t>Contributed surplus, note 11 (c)</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E136" s="5" t="n">
         <v>0.27595</v>
       </c>
@@ -25804,7 +25870,11 @@
           <t>Share-based payments, note 9</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -28304,7 +28374,11 @@
           <t>Amortization, note 8</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -28398,7 +28472,11 @@
           <t>Share-based payments, note 10</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -29068,7 +29146,11 @@
           <t>Purchase of investments, note 6</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -29824,7 +29906,11 @@
           <t>Investments disposed of in settlement of accounts payable, note 6</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -39662,7 +39748,11 @@
           <t>Professional fees, note 10</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -41546,7 +41636,11 @@
           <t>Professional fees, note 11</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -41718,7 +41812,11 @@
           <t>Amortization, note 8</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -43040,7 +43138,11 @@
           <t>Professional fees, note 12</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E374" s="5" t="n">
         <v>0.19109</v>
       </c>
@@ -43304,7 +43406,11 @@
           <t>Amortization, note 9</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -44510,7 +44616,11 @@
           <t>Amortization, note 7</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -45348,7 +45458,11 @@
           <t>Deferred income taxes, note 13</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -45444,7 +45558,11 @@
           <t>Rent, note 10</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
@@ -46012,7 +46130,11 @@
           <t>Deferred income taxes, note 13</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -46394,7 +46516,11 @@
           <t>Professional fees, note 9</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
           <t>-</t>
@@ -46488,7 +46614,11 @@
           <t>Rent, note 9</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -47626,7 +47756,11 @@
           <t>Rent, note 12</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E423" s="5" t="n">
         <v>0.009601999999999999</v>
       </c>
@@ -47910,7 +48044,11 @@
           <t>Future income taxes, note 15</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E426" s="5" t="n">
         <v>0.262</v>
       </c>

--- a/output/pdf_financials_xlsx/PX.xlsx
+++ b/output/pdf_financials_xlsx/PX.xlsx
@@ -6530,10 +6530,10 @@
         <v>0.024547</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>0.003946</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>0.081432</v>
       </c>
     </row>
     <row r="108">
@@ -6732,7 +6732,7 @@
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002626</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
@@ -6903,7 +6903,7 @@
         <v>0</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>0</v>
+        <v>-0.2762</v>
       </c>
       <c r="M114" s="3" t="n">
         <v>-0.033216</v>
@@ -6928,13 +6928,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>2.941809</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>2.588948</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>2.664978</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -6952,25 +6952,25 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.10776</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.314414</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.0844</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.050615</v>
       </c>
       <c r="O115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.073629</v>
       </c>
       <c r="Q115" s="3" t="n">
         <v>0</v>
@@ -8043,7 +8043,7 @@
         <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002626</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>0</v>
@@ -8104,7 +8104,7 @@
         <v>-0.483304</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-0.613725</v>
+        <v>-0.616351</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>-1.172573</v>
@@ -21314,7 +21314,11 @@
           <t>Share-based compensation expense 10,11</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -22848,7 +22852,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -23426,7 +23434,11 @@
           <t>Share-based compensation expense 9</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -26728,7 +26740,11 @@
           <t>Proceeds from disposal of marketable securities</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -27108,7 +27124,11 @@
           <t>Non-brokered private placement, note 8</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -29246,7 +29266,11 @@
           <t>Proceeds from disposal of investments, note 6</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -29528,7 +29552,11 @@
           <t>Non-brokered private placement, note 9</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -31026,7 +31054,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -31218,7 +31250,11 @@
           <t>Proceeds from disposal of marketable securities</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -31502,7 +31538,11 @@
           <t>Non-brokered private placement</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -32230,7 +32270,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -32326,7 +32370,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -32514,7 +32562,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -32610,7 +32662,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -34216,7 +34272,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -34408,7 +34468,11 @@
           <t>Proceeds of sale of marketable securities</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E279" s="5" t="n">
         <v>2.941809</v>
       </c>
@@ -35256,7 +35320,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E288" s="5" t="n">
         <v>-0.262</v>
       </c>
@@ -42184,7 +42252,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -44444,7 +44516,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E388" s="5" t="n">
         <v>0.013817</v>
       </c>
